--- a/host.xlsx
+++ b/host.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22188" windowHeight="8855"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="6">
   <si>
     <t>主机ID</t>
   </si>
@@ -57,7 +57,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -216,8 +216,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,8 +422,28 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -445,16 +471,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF5B9BD5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -516,13 +533,181 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF5B9BD5"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -567,28 +752,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -673,7 +858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -681,6 +866,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="23" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="23" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="23" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1219,8 +1419,8 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="50.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="50.8888888888889"/>
+    <col min="2" max="2" customWidth="true" width="38.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1232,7 +1432,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1256,7 +1456,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1307,7 +1507,7 @@
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
